--- a/Lasser_Driver_v5/pm1p8V_pm5V_5Vref_5Vlaser/pm1p8V_pm5V_5Vref_5Vlaser_BOM_digikey_priced.xlsx
+++ b/Lasser_Driver_v5/pm1p8V_pm5V_5Vref_5Vlaser/pm1p8V_pm5V_5Vref_5Vlaser_BOM_digikey_priced.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -2880,24 +2880,90 @@
       </c>
     </row>
     <row r="40">
-      <c r="L40" s="2" t="n"/>
-      <c r="M40" s="2" t="n"/>
+      <c r="A40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ERJ-6BWFR020V</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Panasonic Industry</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>R42, R43</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20m 1%</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>P.02AQTR-ND</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Panasonic Industry</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>52363</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M40" s="2">
+        <f>L40*J40</f>
+        <v/>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>https://industrial.panasonic.com/cdbs/www-data/pdf/RDO0000/AOA0000C331.pdf</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>LT3045 parallel ballast (was DNP PCB-trace; traces measured ~6mOhm, too low)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="L41" s="3" t="inlineStr">
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="M41" s="3">
-        <f>SUM(M2:M39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Prices pulled 2026-07-13 20:19 (USD), 1 board(s); E1-E6 + VREF_MID (2.5V ratiometric, R50/C75) updates applied 2026-07-14; HS1-HS6 heatsinks + iso kits added 2026-07-14</t>
+      <c r="M42" s="3">
+        <f>SUM(M2:M40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Prices pulled 2026-07-13 20:19 (USD), 1 board(s); E1-E6 + VREF_MID (2.5V ratiometric, R50/C75) updates applied 2026-07-14; HS1-HS6 heatsinks + iso kits added 2026-07-14; R42/R43 20m ballast populated 2026-07-14</t>
         </is>
       </c>
     </row>
